--- a/Requerimientos_EasyOffice.xlsx
+++ b/Requerimientos_EasyOffice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aknuh\OneDrive\Desktop\Git\APT-Capstone_PirqueSpA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aknuh\OneDrive\Desktop\Git\APT-Capstone_EasyOffice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14708D7E-D95C-4879-9FBC-F050693DE504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62A0B55-0596-44A1-AFB4-0C9861BCB4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-180" yWindow="1515" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Léeme" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="205">
   <si>
     <t>Lista de Requerimientos — CRM Easy Office (Capstone APT)</t>
   </si>
@@ -319,15 +319,9 @@
     <t>Registrar qué ejecutivo atendió a qué cliente y qué acciones hizo, para tener seguimiento operativo. Mencionado en la Presentación; NO está en el Informe 1.4.</t>
   </si>
   <si>
-    <t>Por confirmar</t>
-  </si>
-  <si>
     <t>Presentación (no en Informe)</t>
   </si>
   <si>
-    <t>Por confirmar con cliente</t>
-  </si>
-  <si>
     <t>RF-C2</t>
   </si>
   <si>
@@ -358,12 +352,6 @@
     <t>RF-C4</t>
   </si>
   <si>
-    <t>Cobranza</t>
-  </si>
-  <si>
-    <t>Automatizar la cobranza</t>
-  </si>
-  <si>
     <t>La Presentación menciona la cobranza manual como problema; no hay alcance definido para automatizarla en el MVP.</t>
   </si>
   <si>
@@ -638,6 +626,21 @@
   </si>
   <si>
     <t>El MVP debe estar funcionando dentro de las 18 semanas del plazo académico (4 sprints de ~3 semanas, S5–S16).</t>
+  </si>
+  <si>
+    <t>DENEGADO</t>
+  </si>
+  <si>
+    <t>Automatizacion de alerta por cobros y vencimiento</t>
+  </si>
+  <si>
+    <t>Confirmado por Cliente</t>
+  </si>
+  <si>
+    <t>Ajustado, mal definido</t>
+  </si>
+  <si>
+    <t>Rechazado por alcance</t>
   </si>
 </sst>
 </file>
@@ -1600,82 +1603,82 @@
         <v>96</v>
       </c>
       <c r="E22" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F22" s="10" t="s">
-        <v>98</v>
-      </c>
       <c r="G22" s="10" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="D23" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>103</v>
-      </c>
       <c r="E23" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="F23" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>98</v>
-      </c>
       <c r="G23" s="10" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="D24" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="E24" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="F24" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>108</v>
-      </c>
       <c r="G24" s="10" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>111</v>
+        <v>201</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E25" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>98</v>
-      </c>
       <c r="G25" s="10" t="s">
-        <v>99</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -1700,7 +1703,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1728,22 +1731,22 @@
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>25</v>
@@ -1751,22 +1754,22 @@
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>25</v>
@@ -1774,16 +1777,16 @@
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>23</v>
@@ -1797,22 +1800,22 @@
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>25</v>
@@ -1820,16 +1823,16 @@
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>37</v>
@@ -1843,22 +1846,22 @@
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>25</v>
@@ -1866,22 +1869,22 @@
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>25</v>
@@ -1889,22 +1892,22 @@
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>25</v>
@@ -1912,22 +1915,22 @@
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>37</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>25</v>
@@ -1935,22 +1938,22 @@
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>37</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>25</v>
@@ -1958,22 +1961,22 @@
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>37</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>25</v>
@@ -1981,22 +1984,22 @@
     </row>
     <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>37</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>25</v>
@@ -2004,16 +2007,16 @@
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>37</v>
@@ -2027,22 +2030,22 @@
     </row>
     <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>37</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>25</v>
@@ -2050,22 +2053,22 @@
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>37</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>25</v>
@@ -2073,22 +2076,22 @@
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>25</v>
@@ -2096,16 +2099,16 @@
     </row>
     <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>37</v>
@@ -2119,22 +2122,22 @@
     </row>
     <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>25</v>
@@ -2142,16 +2145,16 @@
     </row>
     <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>73</v>
@@ -2165,22 +2168,22 @@
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>25</v>
